--- a/documentation/GESTPROJET_alpa&vall_133.xlsx
+++ b/documentation/GESTPROJET_alpa&vall_133.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduetatfr-my.sharepoint.com/personal/ceyhan_alparslan_studentfr_ch/Documents/Projet 133 - ALP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tvall\Documents\133 final\module-133-classe-300231-valleliant\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{76FEF5ED-6251-4BA4-B3BB-A1E760B79139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1AF6650-CACD-4A93-BB19-61CD07AF28B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB7C011-0BBD-4F79-9EC3-1DA5481FB443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="74">
   <si>
     <t>Planning</t>
   </si>
@@ -348,6 +348,15 @@
   </si>
   <si>
     <t>Ceyhan Alparslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14-15.04.2025 </t>
+  </si>
+  <si>
+    <t>Correction de certains bugs et tests</t>
+  </si>
+  <si>
+    <t>Finalisation du Backend (Correction des bugs) + documentation</t>
   </si>
 </sst>
 </file>
@@ -784,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -861,27 +870,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -904,8 +892,8 @@
     <xf numFmtId="14" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -918,6 +906,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,10 +945,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1230,72 +1238,72 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.85546875" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.81640625" defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
     <col min="2" max="11" width="8" customWidth="1"/>
-    <col min="12" max="17" width="6.5703125" customWidth="1"/>
+    <col min="12" max="17" width="6.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:16" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:16" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="38"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="54"/>
       <c r="L3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="37">
+      <c r="M3" s="53">
         <v>300231</v>
       </c>
-      <c r="N3" s="38"/>
-    </row>
-    <row r="4" spans="1:16" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N3" s="54"/>
+    </row>
+    <row r="4" spans="1:16" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="38"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="54"/>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1303,85 +1311,85 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="34" t="s">
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="34" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="34" t="s">
+      <c r="F7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="34" t="s">
+      <c r="I7" s="51"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="34" t="s">
+      <c r="L7" s="51"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="35"/>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" spans="1:16" s="1" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="51"/>
+      <c r="P7" s="52"/>
+    </row>
+    <row r="8" spans="1:16" s="1" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="46" t="s">
+      <c r="I8" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="48" t="s">
+      <c r="J8" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="45" t="s">
+      <c r="K8" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="46" t="s">
+      <c r="L8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="47" t="s">
+      <c r="M8" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="45" t="s">
+      <c r="N8" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="O8" s="46" t="s">
+      <c r="O8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="47" t="s">
+      <c r="P8" s="40" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>20</v>
       </c>
@@ -1409,28 +1417,28 @@
       <c r="O9" s="29"/>
       <c r="P9" s="30"/>
     </row>
-    <row r="10" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="43"/>
-    </row>
-    <row r="11" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="36"/>
+    </row>
+    <row r="11" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="28"/>
@@ -1453,8 +1461,8 @@
       <c r="O11" s="29"/>
       <c r="P11" s="30"/>
     </row>
-    <row r="12" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+    <row r="12" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="28"/>
@@ -1477,8 +1485,8 @@
       <c r="O12" s="29"/>
       <c r="P12" s="30"/>
     </row>
-    <row r="13" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="28"/>
@@ -1501,8 +1509,8 @@
       <c r="O13" s="29"/>
       <c r="P13" s="30"/>
     </row>
-    <row r="14" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+    <row r="14" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="42" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="28"/>
@@ -1525,8 +1533,8 @@
       <c r="O14" s="29"/>
       <c r="P14" s="30"/>
     </row>
-    <row r="15" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+    <row r="15" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="42" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="28"/>
@@ -1549,28 +1557,28 @@
       <c r="O15" s="29"/>
       <c r="P15" s="30"/>
     </row>
-    <row r="16" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="43"/>
-    </row>
-    <row r="17" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="36"/>
+    </row>
+    <row r="17" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="42" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="28"/>
@@ -1593,8 +1601,8 @@
       <c r="O17" s="29"/>
       <c r="P17" s="30"/>
     </row>
-    <row r="18" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+    <row r="18" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="42" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="28"/>
@@ -1617,8 +1625,8 @@
       <c r="O18" s="29"/>
       <c r="P18" s="30"/>
     </row>
-    <row r="19" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
+    <row r="19" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="42" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="28"/>
@@ -1641,8 +1649,8 @@
       <c r="O19" s="29"/>
       <c r="P19" s="30"/>
     </row>
-    <row r="20" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+    <row r="20" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="42" t="s">
         <v>53</v>
       </c>
       <c r="B20" s="28"/>
@@ -1665,28 +1673,28 @@
       <c r="O20" s="29"/>
       <c r="P20" s="30"/>
     </row>
-    <row r="21" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="43"/>
-    </row>
-    <row r="22" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="36"/>
+    </row>
+    <row r="22" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="42" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="28"/>
@@ -1713,8 +1721,8 @@
       <c r="O22" s="29"/>
       <c r="P22" s="30"/>
     </row>
-    <row r="23" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+    <row r="23" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="42" t="s">
         <v>55</v>
       </c>
       <c r="B23" s="28"/>
@@ -1737,12 +1745,16 @@
       <c r="M23" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="29"/>
+      <c r="N23" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>59</v>
+      </c>
       <c r="P23" s="30"/>
     </row>
-    <row r="24" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
+    <row r="24" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="42" t="s">
         <v>58</v>
       </c>
       <c r="B24" s="28"/>
@@ -1765,32 +1777,38 @@
       <c r="M24" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="N24" s="27"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="30"/>
-    </row>
-    <row r="25" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N24" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="P24" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="30"/>
-    </row>
-    <row r="26" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="36"/>
+    </row>
+    <row r="26" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="42" t="s">
         <v>56</v>
       </c>
       <c r="B26" s="28"/>
@@ -1807,10 +1825,12 @@
       <c r="M26" s="30"/>
       <c r="N26" s="24"/>
       <c r="O26" s="25"/>
-      <c r="P26" s="30"/>
-    </row>
-    <row r="27" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="P26" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="42" t="s">
         <v>57</v>
       </c>
       <c r="B27" s="28"/>
@@ -1827,18 +1847,20 @@
       <c r="M27" s="30"/>
       <c r="N27" s="24"/>
       <c r="O27" s="25"/>
-      <c r="P27" s="30"/>
-    </row>
-    <row r="28" spans="1:16" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
+      <c r="P27" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="14.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="43" t="s">
         <v>63</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
       <c r="D28" s="19"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
       <c r="H28" s="17"/>
       <c r="I28" s="18"/>
       <c r="J28" s="19"/>
@@ -1847,18 +1869,20 @@
       <c r="M28" s="19"/>
       <c r="N28" s="17"/>
       <c r="O28" s="18"/>
-      <c r="P28" s="19"/>
-    </row>
-    <row r="29" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="57" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="18"/>
       <c r="D29" s="19"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="56"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="49"/>
       <c r="H29" s="17"/>
       <c r="I29" s="18"/>
       <c r="J29" s="19"/>
@@ -1866,10 +1890,10 @@
       <c r="L29" s="18"/>
       <c r="M29" s="19"/>
       <c r="N29" s="17"/>
-      <c r="O29" s="44"/>
+      <c r="O29" s="37"/>
       <c r="P29" s="23"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22" t="s">
         <v>22</v>
       </c>
@@ -1877,27 +1901,29 @@
       <c r="C30" s="5"/>
       <c r="D30" s="6"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="51"/>
-      <c r="I30" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="K30" s="51"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="N30" s="51"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="53"/>
+      <c r="F30" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30" s="44"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="44"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="46" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1926,22 +1952,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="63.81640625" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:3" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:3" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1950,7 +1976,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1959,7 +1985,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
@@ -1970,7 +1996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>64</v>
       </c>
@@ -1981,7 +2007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>65</v>
       </c>
@@ -1992,7 +2018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>45747</v>
       </c>
@@ -2003,7 +2029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -2014,92 +2040,104 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="13"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="13"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
+        <v>45775</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="13">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="10"/>
       <c r="C14" s="13"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="10"/>
       <c r="C15" s="13"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="10"/>
       <c r="C16" s="13"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="10"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="10"/>
       <c r="C18" s="13"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="10"/>
       <c r="C19" s="13"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="10"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="10"/>
       <c r="C21" s="13"/>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="13">
         <f>SUM(C8:C21)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" s="16" t="s">
         <v>19</v>
       </c>
@@ -2109,7 +2147,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LModule 133&amp;RJournal de travail</oddHeader>
     <oddFooter>&amp;C&amp;D&amp;R&amp;P/&amp;N</oddFooter>
@@ -2123,22 +2161,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="63.81640625" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:3" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:3" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2147,7 +2185,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2156,7 +2194,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="7" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
@@ -2167,7 +2205,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>64</v>
       </c>
@@ -2178,7 +2216,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>65</v>
       </c>
@@ -2189,7 +2227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>45747</v>
       </c>
@@ -2200,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -2211,92 +2249,104 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="13"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="13"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="12">
+        <v>45768</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="10"/>
       <c r="C14" s="13"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="10"/>
       <c r="C15" s="13"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="10"/>
       <c r="C16" s="13"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="10"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="10"/>
       <c r="C18" s="13"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="10"/>
       <c r="C19" s="13"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="10"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="10"/>
       <c r="C21" s="13"/>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="13">
         <f>SUM(C8:C21)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" s="16" t="s">
         <v>19</v>
       </c>
@@ -2306,7 +2356,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LModule 133&amp;RJournal de travail</oddHeader>
     <oddFooter>&amp;C&amp;D&amp;R&amp;P/&amp;N</oddFooter>
@@ -2315,59 +2365,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Self_Registration_Enabled xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Student_Groups xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <Distribution_Groups xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <AppVersion xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Invited_Teachers xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Templates xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <CultureName xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <LMS_Mappings xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Invited_Students xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <FolderType xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Teachers xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <TeamsChannelId xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Math_Settings xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <Owner xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Students xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3fb344db-9a83-4925-8457-d4a81a8233b7" xsi:nil="true"/>
-    <NotebookType xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2825,28 +2828,65 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Self_Registration_Enabled xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Student_Groups xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <Distribution_Groups xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <AppVersion xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Invited_Teachers xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Templates xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <CultureName xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <LMS_Mappings xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Invited_Students xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <FolderType xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Teachers xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <TeamsChannelId xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Math_Settings xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <Owner xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Students xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3fb344db-9a83-4925-8457-d4a81a8233b7" xsi:nil="true"/>
+    <NotebookType xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="52c6fd7a-766c-4f84-9f35-2a37be325271" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE303A41-7D70-49B7-87A8-C6207A042BC3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE473839-D414-4B78-82BC-08E64CD93726}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3fb344db-9a83-4925-8457-d4a81a8233b7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="52c6fd7a-766c-4f84-9f35-2a37be325271"/>
-    <ds:schemaRef ds:uri="cc3645a1-58b5-4da5-acb4-f681c13b5e81"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2872,9 +2912,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE473839-D414-4B78-82BC-08E64CD93726}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE303A41-7D70-49B7-87A8-C6207A042BC3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="3fb344db-9a83-4925-8457-d4a81a8233b7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="52c6fd7a-766c-4f84-9f35-2a37be325271"/>
+    <ds:schemaRef ds:uri="cc3645a1-58b5-4da5-acb4-f681c13b5e81"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>